--- a/Advence Ms Excel.xlsx
+++ b/Advence Ms Excel.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BHANU SURYAVANSHI\Desktop\Excel Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82EC2A9-5D17-46C2-9436-AEC2CAF4878B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43602F4-2949-42C0-AECB-2A6187024F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{7CB8F25E-5BFA-43E4-B5D8-C68AB5C38C9F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{7CB8F25E-5BFA-43E4-B5D8-C68AB5C38C9F}"/>
   </bookViews>
   <sheets>
     <sheet name="RANDBETWEEN" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet3" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet4" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -76,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="76">
   <si>
     <t>S . No</t>
   </si>
@@ -262,13 +263,55 @@
   </si>
   <si>
     <t>Mixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">science </t>
+  </si>
+  <si>
+    <t xml:space="preserve">english </t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>kabir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sneha </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ritu </t>
+  </si>
+  <si>
+    <t>prcentsge%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">subject </t>
+  </si>
+  <si>
+    <t xml:space="preserve">total </t>
+  </si>
+  <si>
+    <t>subject mm</t>
+  </si>
+  <si>
+    <t>science%</t>
+  </si>
+  <si>
+    <t>english %</t>
+  </si>
+  <si>
+    <t>class total</t>
+  </si>
+  <si>
+    <t>maths %</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -300,12 +343,6 @@
       <color theme="1"/>
       <name val="Consolas"/>
       <family val="3"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -367,7 +404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -401,6 +438,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2456,4 +2511,435 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E4CFA45-514C-48F9-B2E0-4577F138C43B}">
+  <dimension ref="D5:Q18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="3" width="8.88671875" style="16"/>
+    <col min="4" max="4" width="9.21875" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" style="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" style="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.88671875" style="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4" style="16" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="5.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.88671875" style="16"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D5" s="18" t="str">
+        <f>PROPER("name")</f>
+        <v>Name</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="J5" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="K5" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="L5" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+    </row>
+    <row r="6" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D6" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="19">
+        <v>90</v>
+      </c>
+      <c r="F6" s="19">
+        <v>24</v>
+      </c>
+      <c r="G6" s="19">
+        <v>97</v>
+      </c>
+      <c r="H6" s="19">
+        <f>SUM(E6:G6)</f>
+        <v>211</v>
+      </c>
+      <c r="I6" s="19">
+        <f>H6/$H$18*100</f>
+        <v>52.75</v>
+      </c>
+      <c r="J6" s="20">
+        <f>E6/$H6*100</f>
+        <v>42.654028436018962</v>
+      </c>
+      <c r="K6" s="20">
+        <f t="shared" ref="K6:L11" si="0">F6/$H6*100</f>
+        <v>11.374407582938389</v>
+      </c>
+      <c r="L6" s="20">
+        <f t="shared" si="0"/>
+        <v>45.97156398104265</v>
+      </c>
+      <c r="M6" s="21">
+        <f>SUM(J6:L6)</f>
+        <v>100</v>
+      </c>
+      <c r="N6" s="20">
+        <f>E6/E$12*100</f>
+        <v>24.456521739130434</v>
+      </c>
+      <c r="O6" s="20">
+        <f t="shared" ref="O6:P11" si="1">F6/F$12*100</f>
+        <v>8.3916083916083917</v>
+      </c>
+      <c r="P6" s="20">
+        <f t="shared" si="1"/>
+        <v>24.433249370277078</v>
+      </c>
+      <c r="Q6" s="17"/>
+    </row>
+    <row r="7" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D7" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="19">
+        <v>54</v>
+      </c>
+      <c r="F7" s="19">
+        <v>76</v>
+      </c>
+      <c r="G7" s="19">
+        <v>100</v>
+      </c>
+      <c r="H7" s="19">
+        <f t="shared" ref="H7:H11" si="2">SUM(E7:G7)</f>
+        <v>230</v>
+      </c>
+      <c r="I7" s="19">
+        <f t="shared" ref="I7:I11" si="3">H7/$H$18*100</f>
+        <v>57.499999999999993</v>
+      </c>
+      <c r="J7" s="20">
+        <f t="shared" ref="J7:J11" si="4">E7/$H7*100</f>
+        <v>23.478260869565219</v>
+      </c>
+      <c r="K7" s="20">
+        <f t="shared" si="0"/>
+        <v>33.043478260869563</v>
+      </c>
+      <c r="L7" s="20">
+        <f t="shared" si="0"/>
+        <v>43.478260869565219</v>
+      </c>
+      <c r="M7" s="21">
+        <f t="shared" ref="M7:M11" si="5">SUM(J7:L7)</f>
+        <v>100</v>
+      </c>
+      <c r="N7" s="20">
+        <f t="shared" ref="N7:N11" si="6">E7/E$12*100</f>
+        <v>14.673913043478262</v>
+      </c>
+      <c r="O7" s="20">
+        <f t="shared" si="1"/>
+        <v>26.573426573426573</v>
+      </c>
+      <c r="P7" s="20">
+        <f t="shared" si="1"/>
+        <v>25.188916876574307</v>
+      </c>
+      <c r="Q7" s="17"/>
+    </row>
+    <row r="8" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D8" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" s="19">
+        <v>83</v>
+      </c>
+      <c r="F8" s="19">
+        <v>20</v>
+      </c>
+      <c r="G8" s="19">
+        <v>67</v>
+      </c>
+      <c r="H8" s="19">
+        <f t="shared" si="2"/>
+        <v>170</v>
+      </c>
+      <c r="I8" s="19">
+        <f t="shared" si="3"/>
+        <v>42.5</v>
+      </c>
+      <c r="J8" s="20">
+        <f t="shared" si="4"/>
+        <v>48.823529411764703</v>
+      </c>
+      <c r="K8" s="20">
+        <f t="shared" si="0"/>
+        <v>11.76470588235294</v>
+      </c>
+      <c r="L8" s="20">
+        <f t="shared" si="0"/>
+        <v>39.411764705882355</v>
+      </c>
+      <c r="M8" s="21">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="N8" s="20">
+        <f t="shared" si="6"/>
+        <v>22.554347826086957</v>
+      </c>
+      <c r="O8" s="20">
+        <f t="shared" si="1"/>
+        <v>6.9930069930069934</v>
+      </c>
+      <c r="P8" s="20">
+        <f t="shared" si="1"/>
+        <v>16.876574307304786</v>
+      </c>
+      <c r="Q8" s="17"/>
+    </row>
+    <row r="9" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D9" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="19">
+        <v>86</v>
+      </c>
+      <c r="F9" s="19">
+        <v>60</v>
+      </c>
+      <c r="G9" s="19">
+        <v>44</v>
+      </c>
+      <c r="H9" s="19">
+        <f t="shared" si="2"/>
+        <v>190</v>
+      </c>
+      <c r="I9" s="19">
+        <f t="shared" si="3"/>
+        <v>47.5</v>
+      </c>
+      <c r="J9" s="20">
+        <f t="shared" si="4"/>
+        <v>45.263157894736842</v>
+      </c>
+      <c r="K9" s="20">
+        <f t="shared" si="0"/>
+        <v>31.578947368421051</v>
+      </c>
+      <c r="L9" s="20">
+        <f t="shared" si="0"/>
+        <v>23.157894736842106</v>
+      </c>
+      <c r="M9" s="21">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+      <c r="N9" s="20">
+        <f t="shared" si="6"/>
+        <v>23.369565217391305</v>
+      </c>
+      <c r="O9" s="20">
+        <f t="shared" si="1"/>
+        <v>20.97902097902098</v>
+      </c>
+      <c r="P9" s="20">
+        <f t="shared" si="1"/>
+        <v>11.083123425692696</v>
+      </c>
+      <c r="Q9" s="17"/>
+    </row>
+    <row r="10" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D10" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="19">
+        <v>29</v>
+      </c>
+      <c r="F10" s="19">
+        <v>38</v>
+      </c>
+      <c r="G10" s="19">
+        <v>21</v>
+      </c>
+      <c r="H10" s="19">
+        <f t="shared" si="2"/>
+        <v>88</v>
+      </c>
+      <c r="I10" s="19">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="J10" s="20">
+        <f t="shared" si="4"/>
+        <v>32.954545454545453</v>
+      </c>
+      <c r="K10" s="20">
+        <f t="shared" si="0"/>
+        <v>43.18181818181818</v>
+      </c>
+      <c r="L10" s="20">
+        <f t="shared" si="0"/>
+        <v>23.863636363636363</v>
+      </c>
+      <c r="M10" s="21">
+        <f t="shared" si="5"/>
+        <v>99.999999999999986</v>
+      </c>
+      <c r="N10" s="20">
+        <f t="shared" si="6"/>
+        <v>7.8804347826086962</v>
+      </c>
+      <c r="O10" s="20">
+        <f t="shared" si="1"/>
+        <v>13.286713286713287</v>
+      </c>
+      <c r="P10" s="20">
+        <f t="shared" si="1"/>
+        <v>5.2896725440806041</v>
+      </c>
+      <c r="Q10" s="17"/>
+    </row>
+    <row r="11" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D11" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="19">
+        <v>26</v>
+      </c>
+      <c r="F11" s="19">
+        <v>68</v>
+      </c>
+      <c r="G11" s="19">
+        <v>68</v>
+      </c>
+      <c r="H11" s="19">
+        <f t="shared" si="2"/>
+        <v>162</v>
+      </c>
+      <c r="I11" s="19">
+        <f t="shared" si="3"/>
+        <v>40.5</v>
+      </c>
+      <c r="J11" s="20">
+        <f t="shared" si="4"/>
+        <v>16.049382716049383</v>
+      </c>
+      <c r="K11" s="20">
+        <f t="shared" si="0"/>
+        <v>41.975308641975303</v>
+      </c>
+      <c r="L11" s="20">
+        <f t="shared" si="0"/>
+        <v>41.975308641975303</v>
+      </c>
+      <c r="M11" s="21">
+        <f t="shared" si="5"/>
+        <v>99.999999999999986</v>
+      </c>
+      <c r="N11" s="20">
+        <f t="shared" si="6"/>
+        <v>7.0652173913043477</v>
+      </c>
+      <c r="O11" s="20">
+        <f t="shared" si="1"/>
+        <v>23.776223776223777</v>
+      </c>
+      <c r="P11" s="20">
+        <f t="shared" si="1"/>
+        <v>17.128463476070529</v>
+      </c>
+      <c r="Q11" s="17"/>
+    </row>
+    <row r="12" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="D12" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" s="19">
+        <f>SUM(E6:E11)</f>
+        <v>368</v>
+      </c>
+      <c r="F12" s="19">
+        <f t="shared" ref="F12:G12" si="7">SUM(F6:F11)</f>
+        <v>286</v>
+      </c>
+      <c r="G12" s="19">
+        <f t="shared" si="7"/>
+        <v>397</v>
+      </c>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+    </row>
+    <row r="14" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="G14" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="G15" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="H15" s="16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="4:17" x14ac:dyDescent="0.3">
+      <c r="G16" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="H16" s="16">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G17" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="16">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G18" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="H18" s="16">
+        <v>400</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>